--- a/artfynd/A 25237-2025 artfynd.xlsx
+++ b/artfynd/A 25237-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>117140350</v>
       </c>
       <c r="B2" t="n">
-        <v>78478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117140351</v>
+        <v>117140352</v>
       </c>
       <c r="B3" t="n">
-        <v>78444</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607569</v>
+        <v>607347</v>
       </c>
       <c r="R3" t="n">
-        <v>6959336</v>
+        <v>6959319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117140352</v>
+        <v>117140353</v>
       </c>
       <c r="B4" t="n">
-        <v>78478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607347</v>
+        <v>607339</v>
       </c>
       <c r="R4" t="n">
-        <v>6959319</v>
+        <v>6959293</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117140355</v>
+        <v>117140348</v>
       </c>
       <c r="B5" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607588</v>
+        <v>607386</v>
       </c>
       <c r="R5" t="n">
-        <v>6959192</v>
+        <v>6959260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117140348</v>
+        <v>117140351</v>
       </c>
       <c r="B6" t="n">
-        <v>90463</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607386</v>
+        <v>607569</v>
       </c>
       <c r="R6" t="n">
-        <v>6959260</v>
+        <v>6959336</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117140353</v>
+        <v>117140354</v>
       </c>
       <c r="B7" t="n">
-        <v>78478</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607339</v>
+        <v>607600</v>
       </c>
       <c r="R7" t="n">
-        <v>6959293</v>
+        <v>6959173</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,57 +1281,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117140346</v>
+        <v>117140355</v>
       </c>
       <c r="B8" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>storsvedjan, Mpd</t>
+          <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607527</v>
+        <v>607588</v>
       </c>
       <c r="R8" t="n">
-        <v>6959338</v>
+        <v>6959192</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,12 +1385,7 @@
         <v>117140356</v>
       </c>
       <c r="B9" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117140354</v>
+        <v>126675986</v>
       </c>
       <c r="B10" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,34 +1494,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607600</v>
+        <v>607776</v>
       </c>
       <c r="R10" t="n">
-        <v>6959173</v>
+        <v>6959090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,12 +1553,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,15 +1578,218 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126683555</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storsvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>607763</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6959147</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Färska spår</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>117140346</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>storsvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>607527</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6959338</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 25237-2025 artfynd.xlsx
+++ b/artfynd/A 25237-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140350</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140352</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140353</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140348</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140351</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140354</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140355</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140356</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126675986</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126683555</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,8 +1849,26 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>